--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_UnCiv_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_UnCiv_999.xlsx
@@ -2750,7 +2750,7 @@
         <v>142</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>131</v>
